--- a/Result/checksun_type/玻璃纖維_玻纖布.xlsx
+++ b/Result/checksun_type/玻璃纖維_玻纖布.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5050.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4336.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4336.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5777.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6847.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6847</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-351.2719648777975</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5050</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5050.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5616.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4001.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5931.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7423.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7423.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-411.2842611585756</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5616</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5616.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3993.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3993</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5845.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7707.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7707.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-542.9702465183082</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2561</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4282.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4282.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5931.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7956.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7956.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-384.3798596565584</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>35.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3769.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5806.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8223.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8223.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-371.7728834377531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3769</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3769.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>35.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3377.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6107.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8475.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8475.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-242.23531443097</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3377</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3377.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5572.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7861.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7861.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>6235.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9406.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9406.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-6.530383191601686</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5572</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5572.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4007.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7697.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6678.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11379.82</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11379.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>95.24560369291066</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4007</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4007.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.47</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8221.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7579.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7579.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6844.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11648.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11648.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>404.9168133960384</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8221</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8221.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14915.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6624.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6624.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>6226.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12140.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12140.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>381.3429410649342</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14915</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14915.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.96999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6591.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4996.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4996.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>15620.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>15620.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-383.1676958746775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6591</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6591.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>58.46</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>61.85</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>101629.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>186243.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>186243.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>142644.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>229733.22</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>229733.22</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-14558.79496111063</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>101629</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>101629.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>58.91999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>61.99</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.04</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>60.04</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>179513.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>227310.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>227310.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>155827.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>245361.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>245361.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-10206.56370150705</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>179513</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>179513.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>59.81999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>61.79</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>60.01</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>60.01</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>123064.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>199126.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>199126.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>142771.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>260363.94</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>260363.94</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-11969.28462701954</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>123064</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>123064.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>61.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>61.84</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>59.92</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>59.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>237369.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>181271.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>181271.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>136141.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>269928.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>269928.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-8011.875783929572</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>237369</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>237369.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>62.2</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>61.89</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>59.7</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>61.89</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>59.7</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>289642.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>141281.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>141281.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>116001.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>271086.84</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>271086.84</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-14319.26044437499</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>289642</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>289642.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>62.52</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>61.79</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>59.4</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>59.4</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>306964.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>99045.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>99045.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>90421.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>273871.88</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>273871.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-28419.08637199787</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>306964</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>306964.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>64.28</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>61.92</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>59.17</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>59.17</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>38593.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>84344.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>84344.60000000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>65792.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>285738.82</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>285738.82</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-49402.65604103063</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>38593</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>38593.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>64.08</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>61.79</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>58.85</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>58.85</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>33789.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>86415.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>86415.60000000001</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>107552.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>289527.16</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>289527.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-48860.76785246916</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>33789</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>33789.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>63.12</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>61.55</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>58.43</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>58.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>37421.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>91011.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>91011.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>170163.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>291099.54</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>291099.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-45826.90015979318</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>37421</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>37421.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>62.67999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>61.45</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>58.03</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>58.03</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>78459.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>90721.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>90721.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>275716.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>292211.84</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>292211.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-40245.27130740634</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>78459</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>78459.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>62.02</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>61.28</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>57.65</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>57.65</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>233461.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>81798.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>81798</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>339579.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>292447.26</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>292447.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-35231.11325730343</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>233461</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>233461.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>60.98</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>56.35</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>51.53</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>51.53</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>138216.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>115908.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>115908.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>728377.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>263206.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>263206.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-70433.77300886752</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>138216</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>138216.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>61.7</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>55.97</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>51.37</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>51.37</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>44471.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>117355.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>117355.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>811831.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>263098.88</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>263098.88</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-59319.32022713986</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>44471</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>44471.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>61.7</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>55.36</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>51.2</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>62678.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>165228.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>165228.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>838600.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>264395.44</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>264395.44</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-31278.87624513108</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>62678</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>62678.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>62.98</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>54.75</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>51.04</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>51.04</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>118251.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>439156.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>439156.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>837534.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>268227.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>268227.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>7945.253595064743</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>118251</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>118251.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>64.4</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>54.07</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>50.84</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>215928.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>890185.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>890185.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>832864.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>266960.18</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>266960.18</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>57741.71573837788</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>215928</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>215928.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>64.1</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>53.23</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>50.55</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>50.55</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>145451.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1340845.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1340845.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>820014.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>264098.84</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>264098.84</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>116351.9218095975</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>145451</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>145451.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>63.67999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>52.67</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>50.37</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>50.37</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>283835.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1506307.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1506307</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>816570.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>264328.04</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>264328.04</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>203476.4689895684</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>283835</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>283835.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>62.11999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>52.02</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>50.2</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1432317.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1511972.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1511972</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>805992.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>261389.74</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>261389.74</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>305846.2339256137</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1432317</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1432317.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>58.36999999999999</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>51.03</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>49.92</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>49.92</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>2373396.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1235912.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1235912.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>672677.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>238937.7</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>238937.7</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>318114.0326226208</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2373396</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2373396.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>54.25</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>50.04</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>49.66</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>49.66</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>2469228.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>775543.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>775543.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>453816.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>200277.92</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>200277.92</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>223448.3510246803</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2469228</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2469228.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>51.41</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>49.27</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>49.53</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>49.53</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>972759.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>299183.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>299183</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>218238.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>158192.1</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>158192.1</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>69963.65049102658</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>972759</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>972759.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1408.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1390.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1390</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1874.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2505.32</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2505.32</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-162.3915940610709</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1408</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1408.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>897.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1319.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1319.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2147.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2523.66</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2523.66</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-161.590655999162</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>897</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>897.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>61.77</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>2127.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1720.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1720</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2581.7</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2581.7</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-99.92536391075078</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2127</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2127.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>61.72000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>61.82</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>62.15</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>62.15</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1337.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1696.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1696</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2141.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2592.12</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2592.12</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-140.0490407876364</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1337</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1337.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>61.86</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>62.18</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>62.18</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1181.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1820.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1820</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2048.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2632.5</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2632.5</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-107.7239705836289</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1181</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1181.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>61.91</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>62.19</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>62.19</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1057.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>2359.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>2359.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2006.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2638.44</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2638.44</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-40.98372848563167</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1057</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1057.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>61.98</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>61.94</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>2898.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>2974.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>2974.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2218.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2658.94</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2658.94</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>69.10889338599463</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2898</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2898.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>61.98</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2007.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>2693.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>2693.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2055.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2633.78</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2633.78</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>26.66589272453211</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2007</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2007.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>61.8</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>61.99</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1957.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>2586.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>2586.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1968.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2647.68</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2647.68</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>60.54496703942414</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1957</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1957.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>61.7</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>62.03</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3877.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2276.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2276.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1891.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2631.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2631.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>112.1384672378617</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3877</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3877.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>61.6</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>62.08</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>4134.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1653.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1653.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1674.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2583.16</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2583.16</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-23.8757634514368</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>4134</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>4134.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>80.96000000000001</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>80.26</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>72.13</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>72.13</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>4219631.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>6459762.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>6459762.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>10514994.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>7179618.7</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>7179618.7</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-872618.245378321</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>4219631</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>4219631.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>81.3</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>79.92</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>4357828.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6854212.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6854212.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>11379392.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>7283586.76</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>7283586.76</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-616299.2536813151</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>4357828</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>4357828.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>82.32000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>71.65</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>71.65000000000001</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>7263891.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>7386174.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>7386174.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>12186476.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>7452033.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>7452033.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-242925.3993398324</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>7263891</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>7263891.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>78.9</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>71.38</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>71.38</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>9650541.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>8620546.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>8620546.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>12057200.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>7369005.68</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>7369005.68</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-12222.16458986327</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>9650541</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>9650541.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>84.72</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>78.09</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>70.96</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>70.95999999999999</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>6806922.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>9470839.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>9470839</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>12050079.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>7246860.56</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>7246860.56</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>62077.8909311574</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>6806922</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>6806922.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>85.85999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>70.45</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>70.45</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>6191881.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>14570225.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>14570225.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>12705032.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>7234586.06</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>7234586.06</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>470677.224142218</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>6191881</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>6191881.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>88.36</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>76.47</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>70.07</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>70.06999999999999</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>7017636.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>15904572.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>15904572.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>13121669.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>7254854.68</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>7254854.68</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>1103477.906438656</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>7017636</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>7017636.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>88.24</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>75.58</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>69.66</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>69.66</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>13435752.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>16986779.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>16986779.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>13574817.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>7280551.92</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>7280551.92</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>1879595.205917902</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>13435752</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>13435752.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>86.22</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>74.59</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>69.25</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>69.25</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>13902004.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>15493854.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>15493854</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>13423876.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>7316793.2</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>7316793.2</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>2233550.519248325</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>13902004</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>13902004.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>83.42</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>73.54</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>68.86</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>68.86</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>32303855.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>14629320.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>14629320.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>12998241.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>7085175.48</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>7085175.48</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>2609475.73403292</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>32303855</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>32303855.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>80.96000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>72.28</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>72.28</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>68.54000000000001</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>12863617.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>10839839.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>10839839.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>10144922.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>6476342.42</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>6476342.42</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>1081689.30036688</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>12863617</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>12863617.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>32.70999999999999</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>31.34</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>29.26</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>29.26</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1944006554.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>4053080383.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>4053080383.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>5676467276.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>3011039705.48</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>3011039705.48</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-160907096.661325</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1944006554</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1944006554.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>32.66</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>31.18</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>29.17</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>29.17</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>3315121691.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>4039373435.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>4039373435.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>6284234176.8</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>3028757523.46</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>3028757523.46</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>48854436.6204071</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>3315121691</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>3315121691.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>32.33</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>29.08</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>31</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>29.08</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>4137157868.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>3961044951.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>3961044951.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>6620944677.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>3054688543.28</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>3054688543.28</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>199863775.3221531</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>4137157868</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>4137157868.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,21 +25997,17 @@
           <t>32.2</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AM60" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AO60" t="inlineStr">
         <is>
           <t>29.02</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
       <c r="AP60" t="inlineStr">
         <is>
           <t>11.73</t>
@@ -26400,20 +26048,16 @@
           <t>4083852660.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>4401034702.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>4401034702.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>6317087703.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>3126957653.1</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>3126957653.1</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>320378105.3845711</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>4083852660</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>4083852660.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>32.71</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>30.53</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>28.92</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>28.92</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>6785263145.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>5050400120.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>5050400120.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>6125119104.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>3078794968.4</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>3078794968.4</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>486810631.1385765</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>6785263145</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>6785263145.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>33.07</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>30.21</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>28.79</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>28.79</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1875471812.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>7299854170.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>7299854170</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>5834110965.2</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>3017261879.56</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>3017261879.56</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>417748450.5679216</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1875471812</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1875471812.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>33.89</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>28.72</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2923479271.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>8529094918.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>8529094918.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>5813509577.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2995893377.48</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2995893377.48</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>830217676.4824162</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2923479271</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2923479271.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>28.68</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>6337106625.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>9280844403.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>9280844403.799999</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>5742241044.8</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2956155470.54</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2956155470.54</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>1277522283.021608</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>6337106625</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>6337106625.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>33.5</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>29.71</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>28.61</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>7330679748.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>8233140705.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>8233140705</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>5289928427.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2860855797.88</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2860855797.88</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>1505157280.041111</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>7330679748</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>7330679748.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>32.27</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>29.42</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>28.55</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>28.55</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>18032533394.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>7199838088.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>7199838088.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>4838556062.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2729597423.92</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2729597423.92</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>1670140252.603216</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>18032533394</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>18032533394.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>31.1</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>28.53</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>8021675554.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>4368367760.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>4368367760.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>3132042656.8</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2381947504.9</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2381947504.9</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>699555170.8846817</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>8021675554</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>8021675554.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>3512622548</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>6744255965</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>4850127005</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>4661687858</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>10708653199</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>7717712495</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>13894804772</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>12606646015</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>12847401961</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>17904603214</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>8385497650</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
